--- a/joueurs_fusionne.xlsx
+++ b/joueurs_fusionne.xlsx
@@ -667,16 +667,16 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -813,16 +813,16 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -959,16 +959,16 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1105,16 +1105,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
